--- a/artfynd/A 14205-2021 artfynd.xlsx
+++ b/artfynd/A 14205-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14205-2021 artfynd.xlsx
+++ b/artfynd/A 14205-2021 artfynd.xlsx
@@ -1683,12 +1683,7 @@
         <v>94391986</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404720.0846839676</v>
+        <v>404720</v>
       </c>
       <c r="R10" t="n">
-        <v>7014286.091512644</v>
+        <v>7014286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,19 +1756,9 @@
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 14205-2021 artfynd.xlsx
+++ b/artfynd/A 14205-2021 artfynd.xlsx
@@ -1683,7 +1683,7 @@
         <v>94391986</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
